--- a/artfynd/A 20709-2023 artfynd.xlsx
+++ b/artfynd/A 20709-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20709-2023 artfynd.xlsx
+++ b/artfynd/A 20709-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1299,135 +1299,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>112618524</v>
-      </c>
-      <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Slätthult, 300 m NO om gården, Boh</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>307156</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6459570</v>
-      </c>
-      <c r="S7" t="n">
-        <v>50</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Orust</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Torp</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>OB-Oru-0998</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2023-08-22</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2023-08-22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Eftersöktes förgäves på ett halvdussin tidigare kända fläckar. En anledning kan vara att de hamnat under röjda smågranar.</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Olle Molander</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Olle Molander</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20709-2023 artfynd.xlsx
+++ b/artfynd/A 20709-2023 artfynd.xlsx
@@ -790,12 +790,7 @@
         <v>16882815</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>307156.4140347568</v>
+        <v>307156</v>
       </c>
       <c r="R3" t="n">
-        <v>6459570.334975638</v>
+        <v>6459570</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -876,19 +871,9 @@
           <t>2014-08-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-08-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -924,15 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112618662</v>
+        <v>3000068</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,32 +937,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slätthult, 100 m ONO om gården, Boh</t>
+          <t>Slätthult, 500 m NNO om gården, barrskog, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>307044</v>
+        <v>307103</v>
       </c>
       <c r="R4" t="n">
-        <v>6459402</v>
+        <v>6459365</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,22 +974,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>OB-Oru-0038</t>
+          <t>OB-Oru-0865</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>1998-07-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Dellokaler finns åt Ö, SO ovanför brant och åt S.</t>
+          <t>1998-07-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,19 +993,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Olle Molander</t>
+          <t>Bohuslän Floraväktarna</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Molander</t>
+          <t>Bohuslän Floraväktarna, Olle Molander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1053,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112618675</v>
+        <v>112618662</v>
       </c>
       <c r="B5" t="n">
         <v>97650</v>
@@ -1088,7 +1050,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>147</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1101,17 +1063,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Slätthult, 200 m NO om gården, Boh</t>
+          <t>Slätthult, 100 m ONO om gården, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>307121</v>
+        <v>307044</v>
       </c>
       <c r="R5" t="n">
-        <v>6459483</v>
+        <v>6459402</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1135,7 +1097,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>OB-Oru-0039</t>
+          <t>OB-Oru-0038</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1146,6 +1108,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Dellokaler finns åt Ö, SO ovanför brant och åt S.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,7 +1144,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112618701</v>
+        <v>112618675</v>
       </c>
       <c r="B6" t="n">
         <v>97650</v>
@@ -1212,7 +1179,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1225,17 +1192,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slätthult, 500 m NNO om gården, barrskog, Boh</t>
+          <t>Slätthult, 200 m NO om gården, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>307103</v>
+        <v>307121</v>
       </c>
       <c r="R6" t="n">
-        <v>6459365</v>
+        <v>6459483</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,7 +1226,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>OB-Oru-0865</t>
+          <t>OB-Oru-0039</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">

--- a/artfynd/A 20709-2023 artfynd.xlsx
+++ b/artfynd/A 20709-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>16882815</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>3000068</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20709-2023 artfynd.xlsx
+++ b/artfynd/A 20709-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>16882815</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>3000068</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20709-2023 artfynd.xlsx
+++ b/artfynd/A 20709-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>16882815</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>3000068</v>
       </c>
       <c r="B4" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20709-2023 artfynd.xlsx
+++ b/artfynd/A 20709-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>16882815</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>3000068</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20709-2023 artfynd.xlsx
+++ b/artfynd/A 20709-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>16882815</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>3000068</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20709-2023 artfynd.xlsx
+++ b/artfynd/A 20709-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>16882815</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>3000068</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20709-2023 artfynd.xlsx
+++ b/artfynd/A 20709-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>16882815</v>
       </c>
       <c r="B3" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>3000068</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20709-2023 artfynd.xlsx
+++ b/artfynd/A 20709-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>16882815</v>
       </c>
       <c r="B3" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>3000068</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20709-2023 artfynd.xlsx
+++ b/artfynd/A 20709-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>3000067</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>307088.1973847505</v>
+        <v>307088</v>
       </c>
       <c r="R2" t="n">
-        <v>6459352.682372888</v>
+        <v>6459353</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>1998-07-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1998-07-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16882815</v>
+        <v>3000068</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,31 +800,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Slätthult, 300 m NO om gården, Boh</t>
+          <t>Slätthult, 500 m NNO om gården, barrskog, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>307156</v>
+        <v>307103</v>
       </c>
       <c r="R3" t="n">
-        <v>6459570</v>
+        <v>6459365</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,22 +837,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>OB-Oru-0998</t>
+          <t>OB-Oru-0865</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-08-21</t>
+          <t>1998-07-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-08-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ett halvdussin fläckar finns i olika riktningar. 40 st. blommande rosetter.</t>
+          <t>1998-07-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,12 +862,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Olle Molander</t>
+          <t>Bohuslän Floraväktarna</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Molander</t>
+          <t>Bohuslän Floraväktarna, Olle Molander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -909,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3000068</v>
+        <v>16882815</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,20 +906,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slätthult, 500 m NNO om gården, barrskog, Boh</t>
+          <t>Slätthult, 300 m NO om gården, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>307103</v>
+        <v>307156</v>
       </c>
       <c r="R4" t="n">
-        <v>6459365</v>
+        <v>6459570</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,17 +954,22 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>OB-Oru-0865</t>
+          <t>OB-Oru-0998</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1998-07-30</t>
+          <t>2014-08-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1998-07-30</t>
+          <t>2014-08-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ett halvdussin fläckar finns i olika riktningar. 40 st. blommande rosetter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bohuslän Floraväktarna</t>
+          <t>Olle Molander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bohuslän Floraväktarna, Olle Molander</t>
+          <t>Olle Molander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1018,12 +1003,7 @@
         <v>112618662</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,12 +1127,7 @@
         <v>112618675</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 20709-2023 artfynd.xlsx
+++ b/artfynd/A 20709-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3000067</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3000068</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16882815</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112618662</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,8 +1265,20 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112618675</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>